--- a/resources/Part_3_Statistics/S20_L132/4.8.Test-for-the-mean.Independent-samples-Part-1-exercise.xlsx
+++ b/resources/Part_3_Statistics/S20_L132/4.8.Test-for-the-mean.Independent-samples-Part-1-exercise.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21001"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E553E1-9ED5-4175-B40B-DC04DB9D340F}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17250" windowHeight="5580"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="5" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>p-value</t>
   </si>
@@ -138,11 +137,23 @@
   <si>
     <t>Extreme Ajax+</t>
   </si>
+  <si>
+    <t>Std Dev</t>
+  </si>
+  <si>
+    <t>Null Hypoth.</t>
+  </si>
+  <si>
+    <t>Ajax+ cleans less or the same amount of dishes than A</t>
+  </si>
+  <si>
+    <t>We can reject the null Hypothesis with a 2% significance level.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -276,7 +287,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -553,31 +564,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:K22"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="8.88671875" style="1"/>
-    <col min="9" max="9" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="7.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="1"/>
+    <col min="9" max="9" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="12" t="s">
         <v>21</v>
       </c>
@@ -596,7 +607,7 @@
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
     </row>
-    <row r="7" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
@@ -611,7 +622,7 @@
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
     </row>
-    <row r="8" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
@@ -626,7 +637,7 @@
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
     </row>
-    <row r="9" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
@@ -641,7 +652,7 @@
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
     </row>
-    <row r="10" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
         <v>16</v>
       </c>
@@ -656,7 +667,7 @@
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
     </row>
-    <row r="11" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
         <v>17</v>
       </c>
@@ -676,10 +687,10 @@
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
     </row>
-    <row r="13" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="2:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
       <c r="C14" s="4" t="s">
         <v>24</v>
@@ -692,7 +703,7 @@
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
         <v>1</v>
       </c>
@@ -707,7 +718,7 @@
       </c>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
         <v>3</v>
       </c>
@@ -723,7 +734,7 @@
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="2:10" ht="12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="6" t="s">
         <v>6</v>
       </c>
@@ -740,41 +751,68 @@
       <c r="J17" s="3"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="1">
+        <f>SQRT(C17)</f>
+        <v>25</v>
+      </c>
+      <c r="D18" s="1">
+        <f>SQRT(D17)</f>
+        <v>20</v>
+      </c>
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
     </row>
-    <row r="19" spans="2:10" ht="12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
+      <c r="F19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="I19" s="11"/>
       <c r="J19" s="10"/>
     </row>
-    <row r="20" spans="2:10" ht="12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
     </row>
-    <row r="21" spans="2:10" ht="12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
+      <c r="D21" s="9">
+        <f>(E16-0)/SQRT((C17/C15)+(D17/D15))</f>
+        <v>2.3426064283290908</v>
+      </c>
       <c r="I21" s="10"/>
     </row>
-    <row r="22" spans="2:10" ht="12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
+      <c r="D22" s="9">
+        <v>1.915E-2</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="I22" s="10"/>
     </row>
   </sheetData>
